--- a/data/trans_orig/P78C_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P78C_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba la persona sustentadora principal en 2023</t>
+          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba la persona sustentadora principal en 2023 (tasa de respuesta: 98,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>382500</t>
+          <t>382030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>429095</t>
+          <t>429022</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>418827</t>
+          <t>421333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>447591</t>
+          <t>449176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>811883</t>
+          <t>810497</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>865983</t>
+          <t>866225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,28%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>30486</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17897</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>35919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20127</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23949</t>
+          <t>24912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46376</t>
+          <t>46887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24687</t>
+          <t>23735</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40065</t>
+          <t>39290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64752</t>
+          <t>64867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>478</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11720</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96568</t>
+          <t>97263</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137135</t>
+          <t>136982</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64312</t>
+          <t>62005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88966</t>
+          <t>87023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166402</t>
+          <t>168229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215195</t>
+          <t>215674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314891</t>
+          <t>319286</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>795955</t>
+          <t>796793</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>550455</t>
+          <t>548796</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>588693</t>
+          <t>587017</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>754338</t>
+          <t>737627</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1373243</t>
+          <t>1373525</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,48%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36291</t>
+          <t>36891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102344</t>
+          <t>101674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20993</t>
+          <t>20540</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37172</t>
+          <t>38325</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65722</t>
+          <t>63266</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127441</t>
+          <t>127433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1864,97 +1864,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4338</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>1225</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4243</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4312</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4237</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>649373</t>
+          <t>656972</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>807188</t>
+          <t>842579</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68724</t>
+          <t>66773</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14790</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28379</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42595</t>
+          <t>43782</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87486</t>
+          <t>85875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25695</t>
+          <t>25768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,82 +2218,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3705</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9088</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>18046</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>10355</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>28403</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3705</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>8851</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>18046</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>9958</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>29528</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57566</t>
+          <t>55536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>146726</t>
+          <t>148860</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73314</t>
+          <t>75099</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105954</t>
+          <t>105797</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>127243</t>
+          <t>117867</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>237917</t>
+          <t>236202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>463562</t>
+          <t>463497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>508006</t>
+          <t>507862</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>638991</t>
+          <t>637827</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>720520</t>
+          <t>717100</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1110828</t>
+          <t>1111372</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1243460</t>
+          <t>1252616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36639</t>
+          <t>36305</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64151</t>
+          <t>62933</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29038</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>40039</t>
+          <t>39490</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>85236</t>
+          <t>85513</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>458</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,47 +2935,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>9305</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>4246</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>16642</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>9305</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>4672</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>17779</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>17535</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34189</t>
+          <t>35398</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15348</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20793</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48223</t>
+          <t>49645</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80360</t>
+          <t>81013</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63485</t>
+          <t>63157</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>66494</t>
+          <t>62501</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>133100</t>
+          <t>133179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>559823</t>
+          <t>560800</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>610909</t>
+          <t>609640</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>425992</t>
+          <t>442937</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>645848</t>
+          <t>647160</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>990028</t>
+          <t>1002579</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1233772</t>
+          <t>1233301</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,27%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>82364</t>
+          <t>83823</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121730</t>
+          <t>121067</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30790</t>
+          <t>31217</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55328</t>
+          <t>54744</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>119019</t>
+          <t>119710</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>168477</t>
+          <t>168754</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>487</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>18802</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15929</t>
+          <t>16018</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>30936</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>14617</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>31333</t>
+          <t>32618</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12090</t>
+          <t>12243</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>286211</t>
+          <t>253404</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>33501</t>
+          <t>33991</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>359747</t>
+          <t>333262</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>23379</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>27701</t>
+          <t>28131</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>71694</t>
+          <t>73013</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>104905</t>
+          <t>108328</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>59157</t>
+          <t>59887</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>97031</t>
+          <t>98169</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>141430</t>
+          <t>141552</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>196009</t>
+          <t>195278</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1649369</t>
+          <t>1596478</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2276213</t>
+          <t>2276360</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2104567</t>
+          <t>2075468</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2371668</t>
+          <t>2364798</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3716044</t>
+          <t>3782930</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4604112</t>
+          <t>4591892</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>191004</t>
+          <t>185726</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>278556</t>
+          <t>281936</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>72429</t>
+          <t>73254</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>113447</t>
+          <t>114745</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>281965</t>
+          <t>280631</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>382568</t>
+          <t>380516</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4588,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>25435</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4623,12 +4623,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>32399</t>
+          <t>32755</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>27893</t>
+          <t>28073</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>829649</t>
+          <t>953297</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>25922</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>43497</t>
+          <t>44681</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1232232</t>
+          <t>1061249</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>86837</t>
+          <t>87237</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>139227</t>
+          <t>139646</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>58797</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>403699</t>
+          <t>403294</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>167127</t>
+          <t>170672</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>494460</t>
+          <t>553903</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -4927,12 +4927,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>26318</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>55461</t>
+          <t>54130</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>21890</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>40507</t>
+          <t>40674</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>72128</t>
+          <t>71087</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>291968</t>
+          <t>280547</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>425847</t>
+          <t>425486</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>228037</t>
+          <t>220202</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>326012</t>
+          <t>324946</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>551896</t>
+          <t>568641</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>725653</t>
+          <t>727485</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78C_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P78C_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>405630</t>
+          <t>444775</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>382030</t>
+          <t>420625</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>429022</t>
+          <t>467203</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>434793</t>
+          <t>467718</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>421333</t>
+          <t>451986</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>449176</t>
+          <t>482335</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>840423</t>
+          <t>912492</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>810497</t>
+          <t>884970</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>866225</t>
+          <t>941037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>25488</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>16072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30486</t>
+          <t>35049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10429</t>
+          <t>14434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>34320</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>24712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35919</t>
+          <t>45952</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>708</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>452</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,57 +996,57 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>4510</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>4263</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>671</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6547</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17804</t>
+          <t>19764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33578</t>
+          <t>38412</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>28119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46887</t>
+          <t>51516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23735</t>
+          <t>25823</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>50625</t>
+          <t>56169</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39290</t>
+          <t>43336</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64867</t>
+          <t>72657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>844</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>12882</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1403,102 +1403,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>115419</t>
+          <t>123613</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97263</t>
+          <t>104194</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136982</t>
+          <t>143687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>79278</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>67764</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>93582</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>13,73%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>16,2%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>202891</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>179488</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>230484</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>16,61%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,39%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>74505</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>62005</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>87023</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>16,26%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>189924</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>168229</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>215674</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1516,17 +1516,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>585662</t>
+          <t>644108</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>585662</t>
+          <t>644108</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>585662</t>
+          <t>644108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>535178</t>
+          <t>577540</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>535178</t>
+          <t>577540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>535178</t>
+          <t>577540</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1120840</t>
+          <t>1221647</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1120840</t>
+          <t>1221647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1120840</t>
+          <t>1221647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>609223</t>
+          <t>680362</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>319286</t>
+          <t>650629</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>796793</t>
+          <t>709061</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>570423</t>
+          <t>635320</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>548796</t>
+          <t>614196</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>587017</t>
+          <t>654356</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1179646</t>
+          <t>1315682</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>737627</t>
+          <t>1279236</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1373525</t>
+          <t>1350200</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73348</t>
+          <t>80831</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36891</t>
+          <t>64524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101674</t>
+          <t>99600</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28621</t>
+          <t>31411</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20540</t>
+          <t>23767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38325</t>
+          <t>42723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>101969</t>
+          <t>112242</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63266</t>
+          <t>93345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127433</t>
+          <t>133480</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>248374</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>656972</t>
+          <t>14709</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>254713</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>842579</t>
+          <t>20320</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46928</t>
+          <t>49954</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22760</t>
+          <t>37645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66773</t>
+          <t>65233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>24843</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29939</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>67843</t>
+          <t>74798</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43782</t>
+          <t>58954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85875</t>
+          <t>91134</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14341</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25768</t>
+          <t>34590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18046</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10355</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28403</t>
+          <t>37778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>108222</t>
+          <t>119779</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55536</t>
+          <t>98406</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148860</t>
+          <t>141426</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>88070</t>
+          <t>99918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>75099</t>
+          <t>84899</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105797</t>
+          <t>120553</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>196293</t>
+          <t>219697</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>117867</t>
+          <t>192432</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>236202</t>
+          <t>245845</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -2424,17 +2424,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1100437</t>
+          <t>957006</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1100437</t>
+          <t>957006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1100437</t>
+          <t>957006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>719298</t>
+          <t>803691</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>719298</t>
+          <t>803691</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>719298</t>
+          <t>803691</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1819735</t>
+          <t>1760697</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1819735</t>
+          <t>1760697</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1819735</t>
+          <t>1760697</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>486689</t>
+          <t>559790</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>463497</t>
+          <t>534984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>507862</t>
+          <t>583732</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>675851</t>
+          <t>511741</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>637827</t>
+          <t>495350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>717100</t>
+          <t>524781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1162540</t>
+          <t>1071530</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1111372</t>
+          <t>1039605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1252616</t>
+          <t>1097987</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>81,87%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48074</t>
+          <t>56597</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36305</t>
+          <t>42874</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62933</t>
+          <t>72436</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28369</t>
+          <t>29325</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>65543</t>
+          <t>77361</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>39490</t>
+          <t>63315</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>85513</t>
+          <t>96213</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -2767,22 +2767,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13564</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>9574</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>20035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>24681</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17535</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>24110</t>
+          <t>26592</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>18697</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35398</t>
+          <t>37649</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -3106,69 +3106,69 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15348</t>
+          <t>15396</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>3982</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8111</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>1,34%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3790</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8525</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>15</t>
@@ -3176,32 +3176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12298</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20954</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>63117</t>
+          <t>76112</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>49645</t>
+          <t>59883</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>81013</t>
+          <t>94137</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3254,32 +3254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>41877</t>
+          <t>53837</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>43492</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63157</t>
+          <t>67135</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,32 +3289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>104994</t>
+          <t>129949</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62501</t>
+          <t>109126</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>133179</t>
+          <t>153489</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -3332,17 +3332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>634938</t>
+          <t>733729</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>634938</t>
+          <t>733729</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>634938</t>
+          <t>733729</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,17 +3367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>753003</t>
+          <t>607338</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>753003</t>
+          <t>607338</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>753003</t>
+          <t>607338</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1387941</t>
+          <t>1341067</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1387941</t>
+          <t>1341067</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1387941</t>
+          <t>1341067</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>585614</t>
+          <t>629257</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>560800</t>
+          <t>600936</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>609640</t>
+          <t>653614</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>585015</t>
+          <t>635495</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>442937</t>
+          <t>613099</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>647160</t>
+          <t>654933</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1170627</t>
+          <t>1264753</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1002579</t>
+          <t>1231650</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1233301</t>
+          <t>1296935</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>76,45%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>101058</t>
+          <t>105688</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>83823</t>
+          <t>87946</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121067</t>
+          <t>127460</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>43397</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31217</t>
+          <t>38078</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54744</t>
+          <t>61637</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>144455</t>
+          <t>154009</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>119710</t>
+          <t>133880</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>168754</t>
+          <t>177534</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14641</t>
+          <t>15944</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>19453</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -3788,67 +3788,67 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>10255</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>5938</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>19276</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>9177</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>4499</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>16018</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>22479</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13527</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30936</t>
+          <t>33378</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -3901,32 +3901,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>22198</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14617</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32618</t>
+          <t>33138</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3936,32 +3936,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>82919</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>253404</t>
+          <t>23524</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3971,32 +3971,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>105194</t>
+          <t>37398</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>33991</t>
+          <t>27136</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>333262</t>
+          <t>50025</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -4014,22 +4014,22 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>23379</t>
+          <t>24597</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4049,32 +4049,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>20480</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>28131</t>
+          <t>30755</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -4127,32 +4127,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>88580</t>
+          <t>97554</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>73013</t>
+          <t>81555</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>108328</t>
+          <t>117768</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4162,32 +4162,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>80653</t>
+          <t>88690</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>59887</t>
+          <t>75710</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>98169</t>
+          <t>105990</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>169234</t>
+          <t>186244</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>141552</t>
+          <t>162925</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>195278</t>
+          <t>210047</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -4240,17 +4240,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>830831</t>
+          <t>889957</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>830831</t>
+          <t>889957</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>830831</t>
+          <t>889957</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>807764</t>
+          <t>806418</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>807764</t>
+          <t>806418</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>807764</t>
+          <t>806418</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1638594</t>
+          <t>1696375</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1638594</t>
+          <t>1696375</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1638594</t>
+          <t>1696375</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2087155</t>
+          <t>2314184</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1596478</t>
+          <t>2262136</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2276360</t>
+          <t>2367283</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2266081</t>
+          <t>2250273</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2075468</t>
+          <t>2211681</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2364798</t>
+          <t>2283320</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>4353236</t>
+          <t>4564456</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3782930</t>
+          <t>4498822</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4591892</t>
+          <t>4621627</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>243015</t>
+          <t>268604</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>185726</t>
+          <t>237883</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>281936</t>
+          <t>301205</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>95687</t>
+          <t>109329</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>73254</t>
+          <t>93373</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>114745</t>
+          <t>129443</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>338702</t>
+          <t>377932</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>280631</t>
+          <t>345437</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>380516</t>
+          <t>417398</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -4583,32 +4583,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>25435</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4618,32 +4618,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>24190</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>32755</t>
+          <t>35487</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -4696,32 +4696,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>273758</t>
+          <t>34327</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>28073</t>
+          <t>23617</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>953297</t>
+          <t>51389</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>25922</t>
+          <t>29786</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>291017</t>
+          <t>54830</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>44681</t>
+          <t>41707</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1061249</t>
+          <t>72658</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -4809,32 +4809,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>116824</t>
+          <t>125967</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>87237</t>
+          <t>106109</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>139646</t>
+          <t>151678</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4844,32 +4844,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>130947</t>
+          <t>68989</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>56850</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>403294</t>
+          <t>83122</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4879,32 +4879,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>247772</t>
+          <t>194956</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>170672</t>
+          <t>171611</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>553903</t>
+          <t>223804</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -4922,69 +4922,69 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>47891</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>27375</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>54130</t>
+          <t>64960</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>10699</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>24367</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
           <t>0,87%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>14241</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>8501</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>21890</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>71</t>
@@ -4992,32 +4992,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>54190</t>
+          <t>64641</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>40674</t>
+          <t>50422</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>71087</t>
+          <t>84221</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -5035,32 +5035,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>375339</t>
+          <t>417058</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>280547</t>
+          <t>381091</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>425486</t>
+          <t>458619</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5070,32 +5070,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>285105</t>
+          <t>321723</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>220202</t>
+          <t>294697</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>324946</t>
+          <t>351378</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5105,32 +5105,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>660444</t>
+          <t>738781</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>568641</t>
+          <t>691417</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>727485</t>
+          <t>785232</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -5148,17 +5148,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3151867</t>
+          <t>3224800</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3151867</t>
+          <t>3224800</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3151867</t>
+          <t>3224800</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,17 +5183,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2815243</t>
+          <t>2794987</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2815243</t>
+          <t>2794987</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2815243</t>
+          <t>2794987</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,17 +5218,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>5967110</t>
+          <t>6019786</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5967110</t>
+          <t>6019786</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5967110</t>
+          <t>6019786</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
